--- a/artfynd/A 66072-2021 artfynd.xlsx
+++ b/artfynd/A 66072-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66072-2021 artfynd.xlsx
+++ b/artfynd/A 66072-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5209801</v>
+        <v>118274170</v>
       </c>
       <c r="B2" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,16 +704,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>, Vrm</t>
+          <t>Genbäcksängen 350 meter NV om, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419416.2277434304</v>
+        <v>418948</v>
       </c>
       <c r="R2" t="n">
-        <v>6613784.022754816</v>
+        <v>6614116</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15 meter in från grusvägen på körvägens norra sida bland massa lupiner.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,71 +763,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Flora Värmland</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Flora Värmland</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5007765</v>
+        <v>55596145</v>
       </c>
       <c r="B3" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>, Vrm</t>
+          <t>Torsberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419416.2277434304</v>
+        <v>418943</v>
       </c>
       <c r="R3" t="n">
-        <v>6613784.022754816</v>
+        <v>6614123</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +862,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ytterligare ett antal lokaler i Torsberget nära rapporterad fyndplats.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,15 +887,209 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Lars Efraimsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Efraimsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5007765</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Genbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419416</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6613784</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2000-12-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Flora Värmland</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Flora Värmland</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5209801</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Genbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>419416</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6613784</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2000-12-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Flora Värmland</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Flora Värmland</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66072-2021 artfynd.xlsx
+++ b/artfynd/A 66072-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118274170</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55596145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5007765</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,8 +1110,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5209801</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>